--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAdvancedVindicatePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAdvancedVindicatePlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\韩\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2C360A-18C6-422B-AC22-5CB06179808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FC0B97-D21B-4C61-A69E-8B8EC501AAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,17 +128,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,68 +463,71 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="5" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAdvancedVindicatePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAdvancedVindicatePlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FC0B97-D21B-4C61-A69E-8B8EC501AAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5D4A20-0021-46C0-8D1E-33F303B6BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,6 +543,11 @@
     <mergeCell ref="D1:D2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="日期格式错误" sqref="D1:D1048576 E1:E1048576" xr:uid="{72EF6887-9251-45F6-B985-89463F0217A8}">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>